--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2746fa196ce476c0/Desktop/kiosco el tio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="201" documentId="11_F0BF34C6AB674EABCA5660F4A3CFFCC672003DE8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B99619DB-0BD3-43BA-80C6-B8C1B7B89A34}"/>
+  <xr:revisionPtr revIDLastSave="202" documentId="11_F0BF34C6AB674EABCA5660F4A3CFFCC672003DE8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AD8F3835-8350-4C8F-B2E0-F6347557BA73}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Comestibles" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="443">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="442">
   <si>
     <t>CODIGO</t>
   </si>
@@ -1357,9 +1357,6 @@
   </si>
   <si>
     <t>PAN HAMBURGUESA DON YEYO CHICO</t>
-  </si>
-  <si>
-    <t>I</t>
   </si>
   <si>
     <t>SIDIET 250CC</t>
@@ -1411,13 +1408,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1433,10 +1429,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1658,7 +1650,7 @@
         <v>6</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>440</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2100,7 +2092,7 @@
       <c r="B29" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="C29" s="3">
+      <c r="C29">
         <v>4250</v>
       </c>
       <c r="D29" s="1">
@@ -2775,7 +2767,7 @@
       <c r="B72" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="C72" s="3">
+      <c r="C72">
         <v>1400</v>
       </c>
       <c r="D72" s="1">
@@ -3553,7 +3545,7 @@
       <c r="B121" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="C121" s="3">
+      <c r="C121">
         <v>1750</v>
       </c>
       <c r="D121" s="1">
@@ -3849,10 +3841,10 @@
         <f t="shared" ref="A141:A145" si="4">IF(B140&lt;&gt;"", A140+1, "")</f>
         <v>140</v>
       </c>
-      <c r="B141" s="3" t="s">
+      <c r="B141" t="s">
         <v>439</v>
       </c>
-      <c r="C141" s="3">
+      <c r="C141">
         <v>1750</v>
       </c>
       <c r="D141" s="1">
@@ -3865,10 +3857,10 @@
         <f t="shared" si="4"/>
         <v>141</v>
       </c>
-      <c r="B142" s="3" t="s">
-        <v>441</v>
-      </c>
-      <c r="C142" s="3">
+      <c r="B142" t="s">
+        <v>440</v>
+      </c>
+      <c r="C142">
         <v>1400</v>
       </c>
       <c r="D142" s="1">
@@ -3881,10 +3873,10 @@
         <f t="shared" si="4"/>
         <v>142</v>
       </c>
-      <c r="B143" s="3" t="s">
-        <v>442</v>
-      </c>
-      <c r="C143" s="3">
+      <c r="B143" t="s">
+        <v>441</v>
+      </c>
+      <c r="C143">
         <v>1550</v>
       </c>
       <c r="D143" s="1">
@@ -3914,7 +3906,7 @@
     </row>
     <row r="146" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="1" t="str">
-        <f t="shared" ref="A142:A396" si="5">IF(B145&lt;&gt;"", A145+1, "")</f>
+        <f t="shared" ref="A146:A396" si="5">IF(B145&lt;&gt;"", A145+1, "")</f>
         <v/>
       </c>
       <c r="D146" s="1" t="str">
@@ -11130,7 +11122,7 @@
       <c r="B34" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="C34" s="3">
+      <c r="C34">
         <v>2500</v>
       </c>
       <c r="D34" s="1">
@@ -13598,13 +13590,13 @@
         <f t="shared" si="1"/>
         <v>331</v>
       </c>
-      <c r="B60" s="3" t="s">
+      <c r="B60" t="s">
         <v>432</v>
       </c>
-      <c r="C60" s="3">
+      <c r="C60">
         <v>2250</v>
       </c>
-      <c r="D60" s="3">
+      <c r="D60">
         <f t="shared" si="3"/>
         <v>3200</v>
       </c>
@@ -13614,13 +13606,13 @@
         <f t="shared" si="1"/>
         <v>332</v>
       </c>
-      <c r="B61" s="3" t="s">
+      <c r="B61" t="s">
         <v>433</v>
       </c>
-      <c r="C61" s="3">
+      <c r="C61">
         <v>1050</v>
       </c>
-      <c r="D61" s="3">
+      <c r="D61">
         <f t="shared" si="3"/>
         <v>1500</v>
       </c>
@@ -13630,13 +13622,13 @@
         <f t="shared" si="1"/>
         <v>333</v>
       </c>
-      <c r="B62" s="3" t="s">
+      <c r="B62" t="s">
         <v>434</v>
       </c>
-      <c r="C62" s="3">
+      <c r="C62">
         <v>550</v>
       </c>
-      <c r="D62" s="3">
+      <c r="D62">
         <f t="shared" si="3"/>
         <v>800</v>
       </c>
@@ -16195,10 +16187,10 @@
         <f t="shared" si="1"/>
         <v>428</v>
       </c>
-      <c r="B99" s="3" t="s">
+      <c r="B99" t="s">
         <v>435</v>
       </c>
-      <c r="C99" s="3">
+      <c r="C99">
         <v>1100</v>
       </c>
       <c r="D99" s="1">
@@ -16211,10 +16203,10 @@
         <f t="shared" si="1"/>
         <v>429</v>
       </c>
-      <c r="B100" s="3" t="s">
+      <c r="B100" t="s">
         <v>436</v>
       </c>
-      <c r="C100" s="3">
+      <c r="C100">
         <v>1750</v>
       </c>
       <c r="D100" s="1">
@@ -16227,10 +16219,10 @@
         <f t="shared" si="1"/>
         <v>430</v>
       </c>
-      <c r="B101" s="3" t="s">
+      <c r="B101" t="s">
         <v>437</v>
       </c>
-      <c r="C101" s="3">
+      <c r="C101">
         <v>2700</v>
       </c>
       <c r="D101" s="1">
